--- a/data/ticket_routing.xlsx
+++ b/data/ticket_routing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Darpan 2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DD5C9E-AB75-49BF-8B74-267566223E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC5173C-9117-4F6A-8979-D11C43A0ABCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D5055545-A768-4018-B969-D6F46DA62105}"/>
   </bookViews>
@@ -757,7 +757,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8995E7D-6B86-4542-973D-07D90A0DEF31}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F64"/>
   <sheetFormatPr defaultColWidth="65.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -788,7 +787,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>9</v>
       </c>
@@ -808,7 +807,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>11</v>
       </c>
@@ -828,7 +827,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>9</v>
       </c>
@@ -848,7 +847,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>11</v>
       </c>
@@ -868,7 +867,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>9</v>
       </c>
@@ -888,7 +887,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>11</v>
       </c>
@@ -908,7 +907,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>9</v>
       </c>
@@ -928,7 +927,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>11</v>
       </c>
@@ -948,7 +947,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>11</v>
       </c>
@@ -968,7 +967,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>56</v>
       </c>
@@ -988,7 +987,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>55</v>
       </c>
@@ -1008,7 +1007,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>14</v>
       </c>
@@ -1028,7 +1027,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>7</v>
       </c>
@@ -1048,7 +1047,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>6</v>
       </c>
@@ -1068,7 +1067,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>50</v>
       </c>
@@ -1088,7 +1087,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>56</v>
       </c>
@@ -1108,7 +1107,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>55</v>
       </c>
@@ -1128,7 +1127,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>56</v>
       </c>
@@ -1148,7 +1147,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>55</v>
       </c>
@@ -1168,7 +1167,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>51</v>
       </c>
@@ -1188,7 +1187,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>53</v>
       </c>
@@ -1208,7 +1207,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>52</v>
       </c>
@@ -1228,7 +1227,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>53</v>
       </c>
@@ -1248,7 +1247,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>52</v>
       </c>
@@ -1268,7 +1267,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>56</v>
       </c>
@@ -1288,7 +1287,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>55</v>
       </c>
@@ -1308,7 +1307,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>56</v>
       </c>
@@ -1328,7 +1327,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>55</v>
       </c>
@@ -1348,7 +1347,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>56</v>
       </c>
@@ -1368,7 +1367,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>55</v>
       </c>
@@ -1388,7 +1387,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>56</v>
       </c>
@@ -1408,7 +1407,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>55</v>
       </c>
@@ -1428,7 +1427,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>54</v>
       </c>
@@ -1448,7 +1447,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>56</v>
       </c>
@@ -1468,7 +1467,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>55</v>
       </c>
@@ -1488,7 +1487,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>59</v>
       </c>
@@ -1508,7 +1507,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>61</v>
       </c>
@@ -1528,7 +1527,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>61</v>
       </c>
@@ -1548,7 +1547,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>61</v>
       </c>
@@ -1568,7 +1567,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>12</v>
       </c>
@@ -1588,7 +1587,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>16</v>
       </c>
@@ -1608,7 +1607,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>12</v>
       </c>
@@ -1628,7 +1627,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>16</v>
       </c>
@@ -1648,7 +1647,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>12</v>
       </c>
@@ -1668,7 +1667,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>16</v>
       </c>
@@ -1688,7 +1687,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>12</v>
       </c>
@@ -1708,7 +1707,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>16</v>
       </c>
@@ -1728,7 +1727,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>12</v>
       </c>
@@ -1748,7 +1747,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>16</v>
       </c>
@@ -1768,7 +1767,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>56</v>
       </c>
@@ -1788,7 +1787,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>55</v>
       </c>
@@ -1808,7 +1807,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>56</v>
       </c>
@@ -1828,7 +1827,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>55</v>
       </c>
@@ -1848,7 +1847,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>56</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -1888,7 +1887,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -1908,7 +1907,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -1928,7 +1927,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>55</v>
       </c>
@@ -2049,13 +2048,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F64" xr:uid="{C8995E7D-6B86-4542-973D-07D90A0DEF31}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Security"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/ticket_routing.xlsx
+++ b/data/ticket_routing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Darpan 2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC5173C-9117-4F6A-8979-D11C43A0ABCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78DF8D0-A4A8-41F6-A222-C4E0FE099442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D5055545-A768-4018-B969-D6F46DA62105}"/>
   </bookViews>

--- a/data/ticket_routing.xlsx
+++ b/data/ticket_routing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Darpan 2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78DF8D0-A4A8-41F6-A222-C4E0FE099442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E6E75D-D4E7-42BA-8988-6261CD79461C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D5055545-A768-4018-B969-D6F46DA62105}"/>
   </bookViews>

--- a/data/ticket_routing.xlsx
+++ b/data/ticket_routing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Darpan 2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E6E75D-D4E7-42BA-8988-6261CD79461C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23D6D92-2AC9-4548-AD69-2803391A491E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D5055545-A768-4018-B969-D6F46DA62105}"/>
   </bookViews>
